--- a/barnhouse/smeta_barnhouse_pod_kluch.xlsx
+++ b/barnhouse/smeta_barnhouse_pod_kluch.xlsx
@@ -22,7 +22,7 @@
     <sheet name="Прочее" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$I$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$I$106</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Смета'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводка'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Исходные'!$A$4:$D$19</definedName>
@@ -413,12 +413,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сводка'!$B$5:$B$15</f>
+              <f>'Сводка'!$B$5:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сводка'!$C$5:$C$15</f>
+              <f>'Сводка'!$C$5:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.  Перегородки — заполнение и обшивка каркаса (каркас уже стоит)</t>
+          <t>1.  Перегородки — вата в каркас; лист только в с/у (каркас уже стоит)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>между отапливаемыми комнатами, звукоизоляция</t>
+          <t>звук между комнатами; лист с жилой стороны не кладём</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>ГВЛ / ГСП 12.5 мм на перегородки, 2 стороны</t>
+          <t>ГВЛВ 12.5 мм в с/у (стены + потолок)</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>720</v>
+        <v>890</v>
       </c>
       <c r="F7" s="15">
         <f>IF(D7="","",D7*E7)</f>
@@ -915,17 +915,17 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>S обшивки ≈ 88 м² / 3.0 м² + запас</t>
+          <t>вкладка С_у</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>1200×2500</t>
+          <t>1200×2500 влагостойкий</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>жилые стороны под МДФ, с/у — влагостойкий</t>
+          <t>под плитку и краску потолка; жилые перегородки без ГВЛ</t>
         </is>
       </c>
     </row>
@@ -937,19 +937,19 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ГВЛВ 10–12 мм дополнительно в с/у</t>
+          <t>Саморезы, лента, шпаклёвка швов — только с/у</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>лист</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>890</v>
+        <v>2200</v>
       </c>
       <c r="F8" s="10">
         <f>IF(D8="","",D8*E8)</f>
@@ -957,17 +957,17 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>стены+потолок с/у</t>
+          <t>норма на мокрую зону</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>1200×2500 влагостойкий</t>
+          <t>Кнауф / аналог</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>под плитку и покраску потолка</t>
+          <t>не на весь дом: МДФ идёт по обрешётке на стойки</t>
         </is>
       </c>
     </row>
@@ -979,19 +979,19 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Профиль / саморезы / лента / шпаклёвка швов</t>
+          <t>Лента уплотнительная и демпфер к перегородкам</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>6500</v>
+        <v>45</v>
       </c>
       <c r="F9" s="15">
         <f>IF(D9="","",D9*E9)</f>
@@ -999,100 +999,101 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>норма на 90 м² обшивки</t>
+          <t>периметр примыканий</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Кнауф / аналог</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>каркас перегородок уже есть — только крепёж листа</t>
-        </is>
-      </c>
+          <t>поролон / Дихтунгсбанд</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Лента уплотнительная и демпфер к перегородкам</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="F10" s="10">
-        <f>IF(D10="","",D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>периметр примыканий</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>поролон / Дихтунгсбанд</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="17">
-        <f>SUM(F6:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="17">
+        <f>SUM(F6:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2.  Обрешётка и МДФ-панели жилых стен и скатных потолков (с/у и терраса нет)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2.  Обрешётка и МДФ-панели жилых стен и скатных потолков (с/у и терраса нет)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Панель МДФ Союз Классик дуб альпийский 2600×238×6</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D13" s="13">
+        <f>Обшивка!B9</f>
+        <v/>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>260</v>
+      </c>
+      <c r="F13" s="15">
+        <f>IF(D13="","",D13*E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>вкладка Обшивка</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>раб. 0,572 м², уп. 8 шт</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>ориентир 260 ₽/шт; Петрович продаёт поштучно, кратно 8</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Панель МДФ Союз Классик дуб альпийский 2600×238×6</t>
+          <t>Брусок 20×40×3000 сухой (обрешётка)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1101,11 +1102,11 @@
         </is>
       </c>
       <c r="D14" s="8">
-        <f>Обшивка!B9</f>
+        <f>Обшивка!B12</f>
         <v/>
       </c>
       <c r="E14" s="9" t="n">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="F14" s="10">
         <f>IF(D14="","",D14*E14)</f>
@@ -1118,37 +1119,37 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>раб. 0,572 м², уп. 8 шт</t>
+          <t>шаг 400 мм</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>ориентир 260 ₽/шт; Петрович продаёт поштучно, кратно 8</t>
+          <t>по плёнке нар. стен и по листам перегородок</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Брусок 20×40×3000 сухой (обрешётка)</t>
+          <t>Кляймер №3 с гвоздями (под 6 мм)</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>упак 100 шт</t>
         </is>
       </c>
       <c r="D15" s="13">
-        <f>Обшивка!B12</f>
+        <f>CEILING(Обшивка!B13/100,1)</f>
         <v/>
       </c>
       <c r="E15" s="14" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="F15" s="15">
         <f>IF(D15="","",D15*E15)</f>
@@ -1156,42 +1157,37 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>вкладка Обшивка</t>
+          <t>≈8 шт на панель</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>шаг 400 мм</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>по плёнке нар. стен и по листам перегородок</t>
-        </is>
-      </c>
+          <t>кляймер под 6 мм</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Кляймер №3 с гвоздями (под 6 мм)</t>
+          <t>Саморезы 3.5×35 / скобы степлера 6–8 мм</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>упак 100 шт</t>
-        </is>
-      </c>
-      <c r="D16" s="8">
-        <f>CEILING(Обшивка!B13/100,1)</f>
-        <v/>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>71</v>
+        <v>2200</v>
       </c>
       <c r="F16" s="10">
         <f>IF(D16="","",D16*E16)</f>
@@ -1199,37 +1195,37 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>≈8 шт на панель</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>кляймер под 6 мм</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr"/>
+          <t>обрешётка + панели</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>производитель запрещает жидкие гвозди</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Саморезы 3.5×35 / скобы степлера 6–8 мм</t>
+          <t>Угол МДФ универсальный 2600, дуб альпийский</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>2200</v>
+        <v>190</v>
       </c>
       <c r="F17" s="15">
         <f>IF(D17="","",D17*E17)</f>
@@ -1237,25 +1233,25 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>обрешётка + панели</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>производитель запрещает жидкие гвозди</t>
-        </is>
-      </c>
+          <t>внутренние/наружные углы</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Союз в цвет панелей</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Угол МДФ универсальный 2600, дуб альпийский</t>
+          <t>Галтель / потолочный плинтус МДФ 2600 в цвет</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1264,10 +1260,10 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="F18" s="10">
         <f>IF(D18="","",D18*E18)</f>
@@ -1275,12 +1271,12 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>внутренние/наружные углы</t>
+          <t>периметр жилых + конёк</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Союз в цвет панелей</t>
+          <t>закрывает стык панели 2,60 и стену 2,615</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr"/>
@@ -1288,24 +1284,25 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Галтель / потолочный плинтус МДФ 2600 в цвет</t>
+          <t>Плинтус напольный МДФ 60–80 мм + уголки, в цвет</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>22</v>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D19" s="13">
+        <f>Обшивка!B14</f>
+        <v/>
       </c>
       <c r="E19" s="14" t="n">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="F19" s="15">
         <f>IF(D19="","",D19*E19)</f>
@@ -1313,144 +1310,148 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>периметр жилых + конёк</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>закрывает стык панели 2,60 и стену 2,615</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr"/>
+          <t>периметр жилых − двери</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>с/у — плинтус керамический в плитке</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Плинтус напольный МДФ 60–80 мм + уголки, в цвет</t>
+          <t>Нащельник у окон/дверей, расходники</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D20" s="8">
-        <f>Обшивка!B14</f>
-        <v/>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>290</v>
+        <v>3500</v>
       </c>
       <c r="F20" s="10">
         <f>IF(D20="","",D20*E20)</f>
         <v/>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>периметр жилых − двери</t>
-        </is>
-      </c>
+      <c r="G20" s="7" t="inlineStr"/>
       <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>с/у — плинтус керамический в плитке</t>
+          <t>изделия окон и дверей свои, только примыкание</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Нащельник у окон/дверей, расходники</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F21" s="15">
-        <f>IF(D21="","",D21*E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>изделия окон и дверей свои, только примыкание</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="17">
-        <f>SUM(F14:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="17">
+        <f>SUM(F13:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3.  Тёплый пол сухой по всему дому (пол уже утеплён и под плёнкой)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>3.  Тёплый пол сухой по всему дому (пол уже утеплён и под плёнкой)</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Теплораспределительная пластина VALTEC VT.FP.SZ</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D24" s="8">
+        <f>Теплый_пол!B12</f>
+        <v/>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>339</v>
+      </c>
+      <c r="F24" s="10">
+        <f>IF(D24="","",D24*E24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>вкладка Теплый_пол</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>VT.FP.SZ.0125 1000×125</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>кратно 40 шт, шаг 125 мм</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Теплораспределительная пластина VALTEC VT.FP.SZ</t>
+          <t>Труба PEX-a / PERT 16×2 для ТП</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D25" s="13">
-        <f>Теплый_пол!B12</f>
+        <f>Теплый_пол!B14</f>
         <v/>
       </c>
       <c r="E25" s="14" t="n">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="F25" s="15">
         <f>IF(D25="","",D25*E25)</f>
@@ -1458,42 +1459,41 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>вкладка Теплый_пол</t>
+          <t>≈8 м/м² + 10%</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>VT.FP.SZ.0125 1000×125</t>
+          <t>бухта 200 м ×2</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>кратно 40 шт, шаг 125 мм</t>
+          <t>5–6 контуров до 80 м</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Труба PEX-a / PERT 16×2 для ТП</t>
+          <t>Коллектор в сборе с расходомерами, 7 выходов</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D26" s="8">
-        <f>Теплый_пол!B14</f>
-        <v/>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>82</v>
+        <v>18900</v>
       </c>
       <c r="F26" s="10">
         <f>IF(D26="","",D26*E26)</f>
@@ -1501,29 +1501,29 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>≈8 м/м² + 10%</t>
+          <t>Теплый_пол!B15</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>бухта 200 м ×2</t>
+          <t>Valtec / Uponor аналог</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>5–6 контуров до 80 м</t>
+          <t>по числу контуров</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Коллектор в сборе с расходомерами, 7 выходов</t>
+          <t>Шкаф коллекторный встраиваемый</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -1535,37 +1535,33 @@
         <v>1</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>18900</v>
+        <v>4200</v>
       </c>
       <c r="F27" s="15">
         <f>IF(D27="","",D27*E27)</f>
         <v/>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>Теплый_пол!B15</t>
-        </is>
-      </c>
+      <c r="G27" s="12" t="inlineStr"/>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Valtec / Uponor аналог</t>
+          <t>600–800 мм</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>по числу контуров</t>
+          <t>в холле / кухне</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встраиваемый</t>
+          <t>Насосно-смесительный узел для ТП</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1577,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>4200</v>
+        <v>18900</v>
       </c>
       <c r="F28" s="10">
         <f>IF(D28="","",D28*E28)</f>
@@ -1586,74 +1582,70 @@
       <c r="G28" s="7" t="inlineStr"/>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>600–800 мм</t>
+          <t>Valtec Combi / аналог</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>в холле / кухне</t>
+          <t>если котёл без своей погоды</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Насосно-смесительный узел для ТП</t>
+          <t>Евроконус 16×3/4, соединители, отводы</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>18900</v>
+        <v>5200</v>
       </c>
       <c r="F29" s="15">
         <f>IF(D29="","",D29*E29)</f>
         <v/>
       </c>
-      <c r="G29" s="12" t="inlineStr"/>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>Valtec Combi / аналог</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>если котёл без своей погоды</t>
-        </is>
-      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>на 7 петель</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr"/>
+      <c r="I29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Евроконус 16×3/4, соединители, отводы</t>
+          <t>Демпферная лента 8–10 мм</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>5200</v>
+        <v>35</v>
       </c>
       <c r="F30" s="10">
         <f>IF(D30="","",D30*E30)</f>
@@ -1661,143 +1653,151 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>на 7 петель</t>
+          <t>периметр комнат</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>уже есть плёнка пола — лента к стенам</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Демпферная лента 8–10 мм</t>
+          <t>Скотч алюминиевый / фольгированный</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="F31" s="15">
         <f>IF(D31="","",D31*E31)</f>
         <v/>
       </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>периметр комнат</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr"/>
+      <c r="G31" s="12" t="inlineStr"/>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>50 м</t>
+        </is>
+      </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>уже есть плёнка пола — лента к стенам</t>
+          <t>стыки плёнки при монтаже пластин</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Скотч алюминиевый / фольгированный</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>320</v>
-      </c>
-      <c r="F32" s="10">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>50 м</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>стыки плёнки при монтаже пластин</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="17">
-        <f>SUM(F25:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="17">
+        <f>SUM(F24:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>4.  Основание пола и финиш (ламинат не на пластины ТП)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>4.  Финиш пола</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>OSB-3 18 мм / фанера ФСФ 18 мм — черновой настил по лагам</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>лист 2500×1250</t>
+        </is>
+      </c>
+      <c r="D35" s="13">
+        <f>CEILING(Полы!B10*1.08/3.125,1)</f>
+        <v/>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F35" s="15">
+        <f>IF(D35="","",D35*E35)</f>
+        <v/>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>весь отапливаемый пол +8%</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>3.125 м²/лист</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>обнулить, если черновой пол уже есть; плёнка сама по себе не основание</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Ламинат 33 кл. / SPC для тёплого пола</t>
+          <t>Саморезы 4.2×55 к лагам</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D36" s="8">
-        <f>Полы!G5+Полы!G6+Полы!G7+Полы!G8</f>
-        <v/>
+          <t>упак 200 шт</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1290</v>
+        <v>420</v>
       </c>
       <c r="F36" s="10">
         <f>IF(D36="","",D36*E36)</f>
@@ -1805,42 +1805,34 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>вкладка Полы, с запасом</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>толщина 8–10 мм, допуск на ТП</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>жилые + холл</t>
-        </is>
-      </c>
+          <t>черновой настил</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Подложка под ламинат для ТП (тонкая)</t>
+          <t>Фанера ФСФ 12 мм поверх пластин ТП — под ламинат</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>лист 2500×1250</t>
         </is>
       </c>
       <c r="D37" s="13">
-        <f>Полы!G5+Полы!G6+Полы!G7+Полы!G8</f>
+        <f>CEILING((Полы!G5+Полы!G6+Полы!G7+Полы!G8)/3.125,1)</f>
         <v/>
       </c>
       <c r="E37" s="14" t="n">
-        <v>180</v>
+        <v>2190</v>
       </c>
       <c r="F37" s="15">
         <f>IF(D37="","",D37*E37)</f>
@@ -1848,71 +1840,83 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>вкладка Полы</t>
+          <t>жилые с запасом</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>1–2 мм, не фольгированная толстая</t>
+          <t>3.125 м²/лист</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>не режет тепло</t>
+          <t>на этот слой: подложка 1–2 мм и ламинат</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Подложка-гармошка / плёнка подложка</t>
+          <t>ГВЛВ 10 мм, 2 слоя — пол с/у поверх ТП</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>рул</t>
+          <t>лист 1200×2500</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="F38" s="10">
         <f>IF(D38="","",D38*E38)</f>
         <v/>
       </c>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>3.59 м² ×2 слоя + запас</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>3.0 м²/лист</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>под гидроизоляцию и плитку</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Пороги / стык ламинат–плитка</t>
+          <t>Саморезы 3.5×41 + клей по дереву на настил 12 мм</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>650</v>
+        <v>2800</v>
       </c>
       <c r="F39" s="15">
         <f>IF(D39="","",D39*E39)</f>
@@ -1920,194 +1924,194 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
+          <t>фанера жилых + ГВЛВ с/у</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr"/>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>листы вразбежку, не крутить в трубу</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Ламинат 33 кл. / SPC для тёплого пола</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D40" s="8">
+        <f>Полы!G5+Полы!G6+Полы!G7+Полы!G8</f>
+        <v/>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F40" s="10">
+        <f>IF(D40="","",D40*E40)</f>
+        <v/>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>вкладка Полы, с запасом</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>8–10 мм, допуск на ТП</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>класть на фанеру 12 мм, не на пластины</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Подложка под ламинат для ТП (тонкая 1–2 мм)</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D41" s="13">
+        <f>Полы!G5+Полы!G6+Полы!G7+Полы!G8</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="F41" s="15">
+        <f>IF(D41="","",D41*E41)</f>
+        <v/>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>вкладка Полы</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>не фольгированная толстая</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>не режет тепло</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Пороги / стык ламинат–плитка</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(D42="","",D42*E42)</f>
+        <v/>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
           <t>с/у и вход</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>алюминий / Т-профиль</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="n"/>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="17">
-        <f>SUM(F36:F39)</f>
-        <v/>
-      </c>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="17">
+        <f>SUM(F35:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="16" t="n"/>
+      <c r="H43" s="16" t="n"/>
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>5.  Санузел — гидроизоляция, плитка, потолок (МДФ нет)</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>Гидроизоляция обмазочная + лента углов</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F43" s="15">
-        <f>IF(D43="","",D43*E43)</f>
-        <v/>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>вкладка С_у</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>Ceresit CR / Knauf Флэхендихт</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>пол + стены на 2 м</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Плитка настенная</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D44" s="8">
-        <f>'С_у'!D5</f>
-        <v/>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F44" s="10">
-        <f>IF(D44="","",D44*E44)</f>
-        <v/>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>вкладка С_у +12%</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>кафель 250×400 / 200×600</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Керамогранит пола с/у</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D45" s="13">
-        <f>'С_у'!D6</f>
-        <v/>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>1690</v>
-      </c>
-      <c r="F45" s="15">
-        <f>IF(D45="","",D45*E45)</f>
-        <v/>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>вкладка С_у +12%</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>противоскользящий</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>поверх ТП</t>
-        </is>
-      </c>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Клей плиточный эластичный C2 S1 (на ТП)</t>
+          <t>Гидроизоляция обмазочная + лента углов</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>42</v>
+        <v>4200</v>
       </c>
       <c r="F46" s="10">
         <f>IF(D46="","",D46*E46)</f>
@@ -2115,46 +2119,55 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>стены+пол с/у</t>
+          <t>вкладка С_у</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>мешок 25 кг ×3</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr"/>
+          <t>Ceresit CR / Knauf Флэхендихт</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>пол + стены на 2 м</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Затирка + герметик санитарный</t>
+          <t>Плитка настенная</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>1</v>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D47" s="13">
+        <f>'С_у'!D5</f>
+        <v/>
       </c>
       <c r="E47" s="14" t="n">
-        <v>1800</v>
+        <v>1450</v>
       </c>
       <c r="F47" s="15">
         <f>IF(D47="","",D47*E47)</f>
         <v/>
       </c>
-      <c r="G47" s="12" t="inlineStr"/>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>вкладка С_у +12%</t>
+        </is>
+      </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>2 кг затирки + 2 тубы</t>
+          <t>кафель 250×400 / 200×600</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr"/>
@@ -2162,66 +2175,80 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Уголки / раскладка плитки, крестики, клинья</t>
+          <t>Керамогранит пола с/у</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>1</v>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D48" s="8">
+        <f>'С_у'!D6</f>
+        <v/>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1200</v>
+        <v>1690</v>
       </c>
       <c r="F48" s="10">
         <f>IF(D48="","",D48*E48)</f>
         <v/>
       </c>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>вкладка С_у +12%</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>противоскользящий</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>поверх ТП</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Краска влагостойкая на потолок с/у</t>
+          <t>Клей плиточный эластичный C2 S1 (на ТП)</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>л</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>780</v>
+        <v>42</v>
       </c>
       <c r="F49" s="15">
         <f>IF(D49="","",D49*E49)</f>
         <v/>
       </c>
-      <c r="G49" s="12">
-        <f>'С_у'!D7</f>
-        <v/>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>стены+пол с/у</t>
+        </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>2 слоя</t>
+          <t>мешок 25 кг ×3</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr"/>
@@ -2229,24 +2256,24 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Ревизионный люк / лючок</t>
+          <t>Затирка + герметик санитарный</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="F50" s="10">
         <f>IF(D50="","",D50*E50)</f>
@@ -2255,159 +2282,158 @@
       <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="7" t="inlineStr">
         <is>
+          <t>2 кг затирки + 2 тубы</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Уголки / раскладка плитки, крестики, клинья</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F51" s="15">
+        <f>IF(D51="","",D51*E51)</f>
+        <v/>
+      </c>
+      <c r="G51" s="12" t="inlineStr"/>
+      <c r="H51" s="12" t="inlineStr"/>
+      <c r="I51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Краска влагостойкая на потолок с/у</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>л</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="F52" s="10">
+        <f>IF(D52="","",D52*E52)</f>
+        <v/>
+      </c>
+      <c r="G52" s="7">
+        <f>'С_у'!D7</f>
+        <v/>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>2 слоя</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Ревизионный люк / лючок</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F53" s="15">
+        <f>IF(D53="","",D53*E53)</f>
+        <v/>
+      </c>
+      <c r="G53" s="12" t="inlineStr"/>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
           <t>200×200 / 300×300</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I53" s="12" t="inlineStr">
         <is>
           <t>если спрятан коллектор/фильтры</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="16" t="n"/>
-      <c r="B51" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="n"/>
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="17">
-        <f>SUM(F43:F50)</f>
-        <v/>
-      </c>
-      <c r="G51" s="16" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="16" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="17">
+        <f>SUM(F46:F53)</f>
+        <v/>
+      </c>
+      <c r="G54" s="16" t="n"/>
+      <c r="H54" s="16" t="n"/>
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>6.  Сантехника — приборы (трубы в разделе 8)</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Унитаз-компакт с сиденьем микролифт</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>8900</v>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(D54="","",D54*E54)</f>
-        <v/>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>план с/у</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>Душевой поддон 900×900 + ограждение / шторка</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>18900</v>
-      </c>
-      <c r="F55" s="15">
-        <f>IF(D55="","",D55*E55)</f>
-        <v/>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>душ 0.9×0.9 по плану</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>акрил + стекло/шторка</t>
-        </is>
-      </c>
-      <c r="I55" s="12" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Смеситель душ с лейкой / стойкой</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <v>6200</v>
-      </c>
-      <c r="F56" s="10">
-        <f>IF(D56="","",D56*E56)</f>
-        <v/>
-      </c>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Трап душевой / сифон поддона</t>
+          <t>Унитаз-компакт с сиденьем микролифт</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -2419,25 +2445,29 @@
         <v>1</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F57" s="15">
         <f>IF(D57="","",D57*E57)</f>
         <v/>
       </c>
-      <c r="G57" s="12" t="inlineStr"/>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>план с/у</t>
+        </is>
+      </c>
       <c r="H57" s="12" t="inlineStr"/>
       <c r="I57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Раковина + сифон + смеситель</t>
+          <t>Душевой поддон 900×900 + ограждение / шторка</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -2449,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>7800</v>
+        <v>18900</v>
       </c>
       <c r="F58" s="10">
         <f>IF(D58="","",D58*E58)</f>
@@ -2457,21 +2487,25 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>план с/у</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr"/>
+          <t>душ 0.9×0.9 по плану</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>акрил + стекло/шторка</t>
+        </is>
+      </c>
       <c r="I58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Полотенцесушитель водяной или электрический</t>
+          <t>Смеситель душ с лейкой / стойкой</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -2483,67 +2517,55 @@
         <v>1</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>6500</v>
+        <v>6200</v>
       </c>
       <c r="F59" s="15">
         <f>IF(D59="","",D59*E59)</f>
         <v/>
       </c>
       <c r="G59" s="12" t="inlineStr"/>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>электрический проще на сухом ТП</t>
-        </is>
-      </c>
+      <c r="H59" s="12" t="inlineStr"/>
       <c r="I59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Смеситель кухня + сифон мойки</t>
+          <t>Трап душевой / сифон поддона</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>5400</v>
+        <v>2400</v>
       </c>
       <c r="F60" s="10">
         <f>IF(D60="","",D60*E60)</f>
         <v/>
       </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>кухня по плану</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>мойка — в разделе кухня</t>
-        </is>
-      </c>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Фильтр механический + кран шаровый комплект</t>
+          <t>Раковина + сифон + смеситель</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -2555,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>2800</v>
+        <v>7800</v>
       </c>
       <c r="F61" s="15">
         <f>IF(D61="","",D61*E61)</f>
@@ -2563,180 +2585,176 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>ввод воды</t>
+          <t>план с/у</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr"/>
       <c r="I61" s="12" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Полотенцесушитель водяной или электрический</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F62" s="10">
+        <f>IF(D62="","",D62*E62)</f>
+        <v/>
+      </c>
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>электрический проще на сухом ТП</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Фильтр механический + кран шаровый комплект</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F63" s="15">
+        <f>IF(D63="","",D63*E63)</f>
+        <v/>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>ввод воды</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr"/>
+      <c r="I63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="n"/>
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="16" t="n"/>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="17">
-        <f>SUM(F54:F61)</f>
-        <v/>
-      </c>
-      <c r="G62" s="16" t="n"/>
-      <c r="H62" s="16" t="n"/>
-      <c r="I62" s="16" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="17">
+        <f>SUM(F57:F63)</f>
+        <v/>
+      </c>
+      <c r="G64" s="16" t="n"/>
+      <c r="H64" s="16" t="n"/>
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>7.  Источник тепла (дом без радиаторов, только ТП)</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>Электрокотёл 6–8 кВт с насосом</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>28900</v>
-      </c>
-      <c r="F65" s="15">
-        <f>IF(D65="","",D65*E65)</f>
-        <v/>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>теплопотери утеплённого барнхауса ~3–5 кВт</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="inlineStr">
-        <is>
-          <t>Protherm / Эван / Vaillant</t>
-        </is>
-      </c>
-      <c r="I65" s="12" t="inlineStr">
-        <is>
-          <t>можно заменить на тепловой насос — тогда эта строка 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Бойлер / водонагреватель 80 л</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="9" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F66" s="10">
-        <f>IF(D66="","",D66*E66)</f>
-        <v/>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>ГВС на 2 чел. + запас</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>накопительный</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>если котёл двухконтурный — строку обнулить</t>
-        </is>
-      </c>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Группа безопасности + расширительный бак 8–12 л</t>
+          <t>Электрокотёл 6–8 кВт с насосом</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D67" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>5400</v>
+        <v>28900</v>
       </c>
       <c r="F67" s="15">
         <f>IF(D67="","",D67*E67)</f>
         <v/>
       </c>
-      <c r="G67" s="12" t="inlineStr"/>
-      <c r="H67" s="12" t="inlineStr"/>
-      <c r="I67" s="12" t="inlineStr"/>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>теплопотери утеплённого барнхауса ~3–5 кВт</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>Protherm / Эван / Vaillant</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>можно заменить на тепловой насос — тогда эта строка 0</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Труба подачи котёл–коллектор PEX/PP 25 мм + изоляция</t>
+          <t>Бойлер / водонагреватель 80 л</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>145</v>
+        <v>16500</v>
       </c>
       <c r="F68" s="10">
         <f>IF(D68="","",D68*E68)</f>
@@ -2744,21 +2762,29 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>котельная/кухня → коллектор</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr"/>
-      <c r="I68" s="7" t="inlineStr"/>
+          <t>ГВС на 2 чел. + запас</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>накопительный</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>если котёл двухконтурный — строку обнулить</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Краны, грязевик, термоманометр</t>
+          <t>Группа безопасности + расширительный бак 8–12 л</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -2770,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>3200</v>
+        <v>5400</v>
       </c>
       <c r="F69" s="15">
         <f>IF(D69="","",D69*E69)</f>
@@ -2781,119 +2807,111 @@
       <c r="I69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
-      <c r="B70" s="16" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Труба подачи котёл–коллектор PEX/PP 25 мм + изоляция</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="F70" s="10">
+        <f>IF(D70="","",D70*E70)</f>
+        <v/>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>котельная → коллектор</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Краны, грязевик, термоманометр</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F71" s="15">
+        <f>IF(D71="","",D71*E71)</f>
+        <v/>
+      </c>
+      <c r="G71" s="12" t="inlineStr"/>
+      <c r="H71" s="12" t="inlineStr"/>
+      <c r="I71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="n"/>
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C70" s="16" t="n"/>
-      <c r="D70" s="16" t="n"/>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="17">
-        <f>SUM(F65:F69)</f>
-        <v/>
-      </c>
-      <c r="G70" s="16" t="n"/>
-      <c r="H70" s="16" t="n"/>
-      <c r="I70" s="16" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="C72" s="16" t="n"/>
+      <c r="D72" s="16" t="n"/>
+      <c r="E72" s="16" t="n"/>
+      <c r="F72" s="17">
+        <f>SUM(F67:F71)</f>
+        <v/>
+      </c>
+      <c r="G72" s="16" t="n"/>
+      <c r="H72" s="16" t="n"/>
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>8.  Водопровод и канализация внутри дома</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>Труба PPR / PEX 20 мм холод+горяч</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D73" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="E73" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="F73" s="15">
-        <f>IF(D73="","",D73*E73)</f>
-        <v/>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>с/у + кухня + бойлер</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="inlineStr"/>
-      <c r="I73" s="12" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Труба канализация 50 мм + отводы</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>165</v>
-      </c>
-      <c r="F74" s="10">
-        <f>IF(D74="","",D74*E74)</f>
-        <v/>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>умывальник, душ, стиралка, кухня</t>
-        </is>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>серая ПП</t>
-        </is>
-      </c>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Труба канализация 110 мм + тройники</t>
+          <t>Труба PPR / PEX 20 мм холод+горяч</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -2902,10 +2920,10 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="F75" s="15">
         <f>IF(D75="","",D75*E75)</f>
@@ -2913,210 +2931,210 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>унитаз + выпуск</t>
+          <t>с/у + бойлер, без кухни</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr"/>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>выпуск до наружной трубы — внутри дома</t>
-        </is>
-      </c>
+      <c r="I75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Клипсы, хомуты, манжеты, ревизия</t>
+          <t>Труба канализация 50 мм + отводы</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>2100</v>
+        <v>165</v>
       </c>
       <c r="F76" s="10">
         <f>IF(D76="","",D76*E76)</f>
         <v/>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>умывальник, душ, стиралка</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>серая ПП</t>
+        </is>
+      </c>
       <c r="I76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Гибкие подводки 2 шт × 4 точки</t>
+          <t>Труба канализация 110 мм + тройники</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D77" s="13" t="n">
         <v>8</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="F77" s="15">
         <f>IF(D77="","",D77*E77)</f>
         <v/>
       </c>
-      <c r="G77" s="12" t="inlineStr"/>
-      <c r="H77" s="12" t="inlineStr">
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>унитаз + выпуск</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr"/>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>выпуск до наружной трубы — внутри дома</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Клипсы, хомуты, манжеты, ревизия</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F78" s="10">
+        <f>IF(D78="","",D78*E78)</f>
+        <v/>
+      </c>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Гибкие подводки</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="F79" s="15">
+        <f>IF(D79="","",D79*E79)</f>
+        <v/>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>с/у точки</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
         <is>
           <t>40–50 см</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="16" t="n"/>
-      <c r="B78" s="16" t="inlineStr">
+      <c r="I79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="n"/>
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C78" s="16" t="n"/>
-      <c r="D78" s="16" t="n"/>
-      <c r="E78" s="16" t="n"/>
-      <c r="F78" s="17">
-        <f>SUM(F73:F77)</f>
-        <v/>
-      </c>
-      <c r="G78" s="16" t="n"/>
-      <c r="H78" s="16" t="n"/>
-      <c r="I78" s="16" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="C80" s="16" t="n"/>
+      <c r="D80" s="16" t="n"/>
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="17">
+        <f>SUM(F75:F79)</f>
+        <v/>
+      </c>
+      <c r="G80" s="16" t="n"/>
+      <c r="H80" s="16" t="n"/>
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>9.  Электрика</t>
         </is>
       </c>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>Щиток навесной 18 модулей + DIN</t>
-        </is>
-      </c>
-      <c r="C81" s="11" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="14" t="n">
-        <v>3200</v>
-      </c>
-      <c r="F81" s="15">
-        <f>IF(D81="","",D81*E81)</f>
-        <v/>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>холл / кухня</t>
-        </is>
-      </c>
-      <c r="H81" s="12" t="inlineStr"/>
-      <c r="I81" s="12" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Автоматы, УЗО, реле напряжения, нулевые шины</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>9800</v>
-      </c>
-      <c r="F82" s="10">
-        <f>IF(D82="","",D82*E82)</f>
-        <v/>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>свет, розетки, плита, стиралка, котёл, бойлер</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>ABB / IEK / Systeme</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>отдельные линии на мокрые и 3 кВт+</t>
-        </is>
-      </c>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг-LS 3×2.5</t>
+          <t>Щиток навесной 18 модулей + DIN</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>86</v>
+        <v>3200</v>
       </c>
       <c r="F83" s="15">
         <f>IF(D83="","",D83*E83)</f>
@@ -3124,7 +3142,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>розетки</t>
+          <t>холл</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr"/>
@@ -3133,24 +3151,24 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг-LS 3×1.5</t>
+          <t>Автоматы, УЗО, реле напряжения, нулевые шины</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>58</v>
+        <v>8900</v>
       </c>
       <c r="F84" s="10">
         <f>IF(D84="","",D84*E84)</f>
@@ -3158,21 +3176,29 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>освещение</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
+          <t>свет, розетки, стиралка, котёл, бойлер</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>ABB / IEK / Systeme</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>без линии плиты — кухню не закладываем</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг-LS 3×4 (плита / котёл)</t>
+          <t>Кабель ВВГнг-LS 3×2.5</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -3181,10 +3207,10 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="F85" s="15">
         <f>IF(D85="","",D85*E85)</f>
@@ -3192,7 +3218,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>2 линии</t>
+          <t>розетки</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr"/>
@@ -3201,12 +3227,12 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Гофра ПВХ 16–20 мм + клипсы</t>
+          <t>Кабель ВВГнг-LS 3×1.5</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -3215,10 +3241,10 @@
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F86" s="10">
         <f>IF(D86="","",D86*E86)</f>
@@ -3226,67 +3252,67 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>по каркасу</t>
+          <t>освещение</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr"/>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>перегородки уже стоят — тянем в пустотах</t>
-        </is>
-      </c>
+      <c r="I86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Подрозетники</t>
+          <t>Кабель ВВГнг-LS 3×4 (котёл / бойлер)</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="F87" s="15">
         <f>IF(D87="","",D87*E87)</f>
         <v/>
       </c>
-      <c r="G87" s="12" t="inlineStr"/>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>1 линия</t>
+        </is>
+      </c>
       <c r="H87" s="12" t="inlineStr"/>
       <c r="I87" s="12" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Розетки 16А</t>
+          <t>Гофра ПВХ 16–20 мм + клипсы</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E88" s="9" t="n">
         <v>22</v>
-      </c>
-      <c r="E88" s="9" t="n">
-        <v>240</v>
       </c>
       <c r="F88" s="10">
         <f>IF(D88="","",D88*E88)</f>
@@ -3294,25 +3320,25 @@
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>по комнатам + кухня + с/у IP44</t>
+          <t>по каркасу</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>без техники</t>
+          <t>перегородки уже стоят — тянем в пустотах</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Выключатели / проходные</t>
+          <t>Подрозетники</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -3321,10 +3347,10 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>260</v>
+        <v>28</v>
       </c>
       <c r="F89" s="15">
         <f>IF(D89="","",D89*E89)</f>
@@ -3337,12 +3363,12 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Светильники потолочные / трек (жилые)</t>
+          <t>Розетки 16А</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -3351,10 +3377,10 @@
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>1900</v>
+        <v>240</v>
       </c>
       <c r="F90" s="10">
         <f>IF(D90="","",D90*E90)</f>
@@ -3362,25 +3388,25 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>скатный потолок — накладные / шина</t>
+          <t>по комнатам + с/у IP44</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>можно заменить своими</t>
+          <t>без кухонного блока</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Светильник с/у IP44 + подсветка зеркала</t>
+          <t>Выключатели / проходные</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -3389,10 +3415,10 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>1600</v>
+        <v>260</v>
       </c>
       <c r="F91" s="15">
         <f>IF(D91="","",D91*E91)</f>
@@ -3405,12 +3431,12 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Вентилятор с/у Ø100 с обратным клапаном</t>
+          <t>Светильники потолочные / трек (жилые)</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -3419,10 +3445,10 @@
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="F92" s="10">
         <f>IF(D92="","",D92*E92)</f>
@@ -3430,37 +3456,37 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>в стену / через кровлю</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>вытяжка</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="inlineStr"/>
+          <t>скатный потолок — накладные / шина</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>можно заменить своими</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Воздуховод 100 мм + решётка + герметик</t>
+          <t>Светильник с/у IP44 + подсветка зеркала</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="F93" s="15">
         <f>IF(D93="","",D93*E93)</f>
@@ -3473,147 +3499,143 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Клеммы WAGO, изолента, маркировка</t>
+          <t>Вентилятор с/у Ø100 с обратным клапаном</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="F94" s="10">
         <f>IF(D94="","",D94*E94)</f>
         <v/>
       </c>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>в стену / через кровлю</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>вытяжка</t>
+        </is>
+      </c>
       <c r="I94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
-      <c r="B95" s="16" t="inlineStr">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>9.13</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Воздуховод 100 мм + решётка + герметик</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F95" s="15">
+        <f>IF(D95="","",D95*E95)</f>
+        <v/>
+      </c>
+      <c r="G95" s="12" t="inlineStr"/>
+      <c r="H95" s="12" t="inlineStr"/>
+      <c r="I95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Клеммы WAGO, изолента, маркировка</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F96" s="10">
+        <f>IF(D96="","",D96*E96)</f>
+        <v/>
+      </c>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="n"/>
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C95" s="16" t="n"/>
-      <c r="D95" s="16" t="n"/>
-      <c r="E95" s="16" t="n"/>
-      <c r="F95" s="17">
-        <f>SUM(F81:F94)</f>
-        <v/>
-      </c>
-      <c r="G95" s="16" t="n"/>
-      <c r="H95" s="16" t="n"/>
-      <c r="I95" s="16" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>10.  Кухня — встроенные материалы (гарнитур целиком можно заменить одной строкой)</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Мойка врезная нерж. 600 мм</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F98" s="10">
-        <f>IF(D98="","",D98*E98)</f>
-        <v/>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>план кухни</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
+      <c r="C97" s="16" t="n"/>
+      <c r="D97" s="16" t="n"/>
+      <c r="E97" s="16" t="n"/>
+      <c r="F97" s="17">
+        <f>SUM(F83:F96)</f>
+        <v/>
+      </c>
+      <c r="G97" s="16" t="n"/>
+      <c r="H97" s="16" t="n"/>
+      <c r="I97" s="16" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>Столешница 38 мм, 2.4 м + пристенный бортик</t>
-        </is>
-      </c>
-      <c r="C99" s="11" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D99" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="14" t="n">
-        <v>9800</v>
-      </c>
-      <c r="F99" s="15">
-        <f>IF(D99="","",D99*E99)</f>
-        <v/>
-      </c>
-      <c r="G99" s="12" t="inlineStr">
-        <is>
-          <t>кухня 2.4 м по плану</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="inlineStr">
-        <is>
-          <t>влагостойкая</t>
-        </is>
-      </c>
-      <c r="I99" s="12" t="inlineStr"/>
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>10.  Прочее и расходники</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Фартук плитка / панель 2.4×0.6 м</t>
+          <t>Пена, герметик акрил/силикон, клей жидкие гвозди</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -3625,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>4500</v>
+        <v>2800</v>
       </c>
       <c r="F100" s="10">
         <f>IF(D100="","",D100*E100)</f>
@@ -3633,33 +3655,29 @@
       </c>
       <c r="G100" s="7" t="inlineStr"/>
       <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
-        <is>
-          <t>если панель — без клея плитки</t>
-        </is>
-      </c>
+      <c r="I100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Варочная панель электрическая 60 см (если нет своей)</t>
+          <t>Грунтовка универсальная + влагостойкая</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>л</t>
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>14500</v>
+        <v>220</v>
       </c>
       <c r="F101" s="15">
         <f>IF(D101="","",D101*E101)</f>
@@ -3667,37 +3685,33 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>план: плита</t>
+          <t>ГВЛ, с/у</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr"/>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>обнулите, если техника своя</t>
-        </is>
-      </c>
+      <c r="I101" s="12" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Вытяжка 60 см + воздуховод</t>
+          <t>Плёнка укрывная, скотч малярный, мешки</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F102" s="10">
         <f>IF(D102="","",D102*E102)</f>
@@ -3707,238 +3721,106 @@
       <c r="H102" s="7" t="inlineStr"/>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>обнулите, если своя</t>
+          <t>для отделки, не строительная пароизоляция</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
-      <c r="B103" s="16" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Крепёж смешанный (анкера, уголки, дюбели)</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F103" s="15">
+        <f>IF(D103="","",D103*E103)</f>
+        <v/>
+      </c>
+      <c r="G103" s="12" t="inlineStr"/>
+      <c r="H103" s="12" t="inlineStr"/>
+      <c r="I103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="n"/>
+      <c r="B104" s="16" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="C103" s="16" t="n"/>
-      <c r="D103" s="16" t="n"/>
-      <c r="E103" s="16" t="n"/>
-      <c r="F103" s="17">
-        <f>SUM(F98:F102)</f>
-        <v/>
-      </c>
-      <c r="G103" s="16" t="n"/>
-      <c r="H103" s="16" t="n"/>
-      <c r="I103" s="16" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>11.  Прочее и расходники</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="5" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="n"/>
+      <c r="C104" s="16" t="n"/>
+      <c r="D104" s="16" t="n"/>
+      <c r="E104" s="16" t="n"/>
+      <c r="F104" s="17">
+        <f>SUM(F100:F103)</f>
+        <v/>
+      </c>
+      <c r="G104" s="16" t="n"/>
+      <c r="H104" s="16" t="n"/>
+      <c r="I104" s="16" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Пена, герметик акрил/силикон, клей жидкие гвозди</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="9" t="n">
-        <v>2800</v>
-      </c>
-      <c r="F106" s="10">
-        <f>IF(D106="","",D106*E106)</f>
-        <v/>
-      </c>
-      <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr"/>
-      <c r="I106" s="7" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>Грунтовка универсальная + влагостойкая</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr">
-        <is>
-          <t>л</t>
-        </is>
-      </c>
-      <c r="D107" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E107" s="14" t="n">
-        <v>220</v>
-      </c>
-      <c r="F107" s="15">
-        <f>IF(D107="","",D107*E107)</f>
-        <v/>
-      </c>
-      <c r="G107" s="12" t="inlineStr">
-        <is>
-          <t>ГВЛ, с/у</t>
-        </is>
-      </c>
-      <c r="H107" s="12" t="inlineStr"/>
-      <c r="I107" s="12" t="inlineStr"/>
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>ИТОГО МАТЕРИАЛЫ (без работ, без окон/дверей/террасы/утепления контура)</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="n"/>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="19">
+        <f>F10+F21+F32+F43+F54+F64+F72+F80+F97+F104</f>
+        <v/>
+      </c>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Плёнка укрывная, скотч малярный, мешки</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F108" s="10">
-        <f>IF(D108="","",D108*E108)</f>
-        <v/>
-      </c>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr"/>
-      <c r="I108" s="7" t="inlineStr">
-        <is>
-          <t>для отделки, не строительная пароизоляция</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>Крепёж смешанный (анкера, уголки, дюбели)</t>
-        </is>
-      </c>
-      <c r="C109" s="11" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D109" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F109" s="15">
-        <f>IF(D109="","",D109*E109)</f>
-        <v/>
-      </c>
-      <c r="G109" s="12" t="inlineStr"/>
-      <c r="H109" s="12" t="inlineStr"/>
-      <c r="I109" s="12" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="16" t="n"/>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>Итого по разделу</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="16" t="n"/>
-      <c r="E110" s="16" t="n"/>
-      <c r="F110" s="17">
-        <f>SUM(F106:F109)</f>
-        <v/>
-      </c>
-      <c r="G110" s="16" t="n"/>
-      <c r="H110" s="16" t="n"/>
-      <c r="I110" s="16" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="18" t="inlineStr">
-        <is>
-          <t>ИТОГО МАТЕРИАЛЫ (без работ, без окон/дверей/террасы/утепления контура)</t>
-        </is>
-      </c>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="19">
-        <f>F11+F22+F33+F40+F51+F62+F70+F78+F95+F103+F110</f>
-        <v/>
-      </c>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>Как пользоваться: меняйте столбец «Цена, ₽» — сумма раздела и итог пересчитаются. Количество с формулой тянется с вкладок Полы / Стены / Потолки / Обшивка / Теплый_пол / С_у. Строки техники (котёл, бойлер, варочная, вытяжка) обнулите в «Кол-во», если привезёте своё. Работы, окна, двери, утепление и плёнка наружного контура, каркасы перегородок и вся терраса в смету не входят. Цены — ориентир Петрович СПб / Valtec, сентябрь 2026; перед закупкой сверьте карточку товара. Отделка: МДФ дуб альпийский 2600×238×6 (Союз), без лака — покрытие уже на панели. Кухня: гарнитур целиком не заложен, только мойка, столешница, фартук и базовая техника.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>Как пользоваться: меняйте столбец «Цена, ₽» — сумма раздела и итог пересчитаются. Количество с формулой тянется с вкладок Полы / Стены / Потолки / Обшивка / Теплый_пол / С_у. Строки техники (котёл, бойлер) обнулите в «Кол-во», если привезёте своё. Работы, окна, двери, утепление и плёнка наружного контура, каркасы перегородок и вся терраса в смету не входят. Цены — ориентир Петрович СПб / Valtec, сентябрь 2026; перед закупкой сверьте карточку товара. Отделка: МДФ дуб альпийский 2600×238×6 (Союз), без лака — покрытие уже на панели. Кухня (гарнитур, мойка, плита, вытяжка, смеситель) в смету не входит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
   </sheetData>
-  <autoFilter ref="A4:I112"/>
-  <mergeCells count="15">
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="A97:I97"/>
+  <autoFilter ref="A4:I106"/>
+  <mergeCells count="14">
+    <mergeCell ref="A82:I82"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="A108:I114"/>
+    <mergeCell ref="A99:I99"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A114:I120"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A106:E106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4618,7 +4500,7 @@
     <row r="17">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>Пластина VT.FP.SZ.0125 = 1000×125 мм, труба Ø16. Пачка 40 шт. Норма 6.4 шт/м² ≈ 80% покрытия (на петлях пластин нет). Контур не длиннее 80–90 м — отсюда число петель. Пол уже утеплён и под плёнкой: подложку под пластины не закладывал.</t>
+          <t>Пластина VT.FP.SZ.0125 = 1000×125 мм, труба Ø16. Пачка 40 шт. Норма 6.4 шт/м² ≈ 80% покрытия (на петлях пластин нет). Контур не длиннее 80–90 м — отсюда число петель. Пол уже утеплён и под плёнкой: подложку под пластины не закладывал. Сверху на пластины — фанера 12 мм (жилые) / ГВЛВ (с/у), затем финиш. Не класть ламинат на пластины.</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5324,15 +5206,15 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>1. Перегородки — заполнение и обшивка</t>
+          <t>1. Перегородки — вата + ГВЛВ с/у</t>
         </is>
       </c>
       <c r="C5" s="14">
-        <f>Смета!F11</f>
+        <f>Смета!F10</f>
         <v/>
       </c>
       <c r="D5" s="22">
-        <f>IF($C$17=0,0,C5/$C$17)</f>
+        <f>IF($C$16=0,0,C5/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5346,11 +5228,11 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>Смета!F22</f>
+        <f>Смета!F21</f>
         <v/>
       </c>
       <c r="D6" s="24">
-        <f>IF($C$17=0,0,C6/$C$17)</f>
+        <f>IF($C$16=0,0,C6/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5364,11 +5246,11 @@
         </is>
       </c>
       <c r="C7" s="14">
-        <f>Смета!F33</f>
+        <f>Смета!F32</f>
         <v/>
       </c>
       <c r="D7" s="22">
-        <f>IF($C$17=0,0,C7/$C$17)</f>
+        <f>IF($C$16=0,0,C7/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5378,15 +5260,15 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>4. Финиш пола</t>
+          <t>4. Настил пола и ламинат</t>
         </is>
       </c>
       <c r="C8" s="9">
-        <f>Смета!F40</f>
+        <f>Смета!F43</f>
         <v/>
       </c>
       <c r="D8" s="24">
-        <f>IF($C$17=0,0,C8/$C$17)</f>
+        <f>IF($C$16=0,0,C8/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5400,11 +5282,11 @@
         </is>
       </c>
       <c r="C9" s="14">
-        <f>Смета!F51</f>
+        <f>Смета!F54</f>
         <v/>
       </c>
       <c r="D9" s="22">
-        <f>IF($C$17=0,0,C9/$C$17)</f>
+        <f>IF($C$16=0,0,C9/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5418,11 +5300,11 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>Смета!F62</f>
+        <f>Смета!F64</f>
         <v/>
       </c>
       <c r="D10" s="24">
-        <f>IF($C$17=0,0,C10/$C$17)</f>
+        <f>IF($C$16=0,0,C10/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5436,11 +5318,11 @@
         </is>
       </c>
       <c r="C11" s="14">
-        <f>Смета!F70</f>
+        <f>Смета!F72</f>
         <v/>
       </c>
       <c r="D11" s="22">
-        <f>IF($C$17=0,0,C11/$C$17)</f>
+        <f>IF($C$16=0,0,C11/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5454,11 +5336,11 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>Смета!F78</f>
+        <f>Смета!F80</f>
         <v/>
       </c>
       <c r="D12" s="24">
-        <f>IF($C$17=0,0,C12/$C$17)</f>
+        <f>IF($C$16=0,0,C12/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5472,11 +5354,11 @@
         </is>
       </c>
       <c r="C13" s="14">
-        <f>Смета!F95</f>
+        <f>Смета!F97</f>
         <v/>
       </c>
       <c r="D13" s="22">
-        <f>IF($C$17=0,0,C13/$C$17)</f>
+        <f>IF($C$16=0,0,C13/$C$16)</f>
         <v/>
       </c>
     </row>
@@ -5486,66 +5368,48 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>10. Кухня — встроенное</t>
+          <t>10. Прочее и расходники</t>
         </is>
       </c>
       <c r="C14" s="9">
-        <f>Смета!F103</f>
+        <f>Смета!F104</f>
         <v/>
       </c>
       <c r="D14" s="24">
-        <f>IF($C$17=0,0,C14/$C$17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>11. Прочее и расходники</t>
-        </is>
-      </c>
-      <c r="C15" s="14">
-        <f>Смета!F110</f>
-        <v/>
-      </c>
-      <c r="D15" s="22">
-        <f>IF($C$17=0,0,C15/$C$17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="25" t="inlineStr">
+        <f>IF($C$16=0,0,C14/$C$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Итого материалы</t>
         </is>
       </c>
-      <c r="C17" s="26">
-        <f>Смета!F112</f>
-        <v/>
-      </c>
-      <c r="D17" s="27">
-        <f>SUM(D5:D15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Не входит в итог: работы; окна; двери; утеплитель и плёнка наружных стен, пола и потолка; каркасы перегородок; любые материалы на террасу. Гарнитур кухни, мебель, шторы, бытовая техника сверх строк 10.4–10.5 — отдельно.</t>
-        </is>
-      </c>
-    </row>
+      <c r="C16" s="26">
+        <f>Смета!F106</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>SUM(D5:D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Не входит в итог: работы; окна; двери; утеплитель и плёнка наружных стен, пола и потолка; каркасы перегородок; терраса; кухня (гарнитур, мойка, плита, вытяжка). Ламинат кладётся на фанеру 12 мм поверх пластин ТП, не на пластины.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20"/>
     <row r="21"/>
-    <row r="22"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A19:D22"/>
+    <mergeCell ref="A18:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5971,7 +5835,7 @@
     <row r="31">
       <c r="A31" s="34" t="inlineStr">
         <is>
-          <t>Заполнение и обшивка каркасов перегородок</t>
+          <t>Заполнение перегородок минватой; МДФ сразу на обрешётку каркаса. ГВЛВ только в с/у под плитку</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5856,7 @@
     <row r="34">
       <c r="A34" s="34" t="inlineStr">
         <is>
-          <t>Финиш пола: ламинат в жилых, плитка в с/у</t>
+          <t>Пирог пола: черновой настил → пластины ТП → фанера 12 мм → подложка → ламинат; в с/у ГВЛВ + плитка</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6387,7 +6251,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Утеплитель и плёнка уже лежат. Считаем только тёплый пол и финиш.</t>
+          <t>Утеплитель и плёнка уже лежат. Ламинат не на пластины: нужен сплошной настил.</t>
         </is>
       </c>
     </row>
@@ -6622,15 +6486,25 @@
     <row r="15">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>Пирог, который уже сделан: лаги/основание + утеплитель + плёнка. Дальше: теплораспределительные пластины VT.FP.SZ + труба 16 мм + финиш. Под кухонный низ можно не класть пластины (~1.8 м²) — на коробку не влияет.</t>
+          <t>Пирог дальше уже сделанного (лаги + утеплитель + плёнка):
+1) Черновой настил OSB-3 / фанера ФСФ 18 мм по лагам — если под плёнкой ещё дырки между лагами. Если черновой пол уже лежит — эту строку в смете обнулить.
+2) Пластины VT.FP.SZ + труба 16 мм (вкладка Теплый_пол).
+3) Сплошной настил поверх пластин: фанера ФСФ 12 мм в жилых — на НЕЁ кладётся тонкая подложка и ламинат. Прямо на алюминиевые пластины ламинат нельзя: трубы и кромки плит продавят замки.
+4) В с/у поверх труб — 2 слоя ГВЛВ 10 мм, затем гидроизоляция и плитка.
+5) Подложка под ламинат только 1–2 мм «для ТП», без толстой пробки.</t>
         </is>
       </c>
     </row>
     <row r="16"/>
     <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A15:G17"/>
+    <mergeCell ref="A15:G22"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/barnhouse/smeta_barnhouse_pod_kluch.xlsx
+++ b/barnhouse/smeta_barnhouse_pod_kluch.xlsx
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>OSB-3 18 мм / фанера ФСФ 18 мм — черновой настил по лагам</t>
+          <t>OSB-3 22 мм — черновой настил по лагам</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -1755,7 +1755,7 @@
         <v/>
       </c>
       <c r="E35" s="14" t="n">
-        <v>1650</v>
+        <v>2150</v>
       </c>
       <c r="F35" s="15">
         <f>IF(D35="","",D35*E35)</f>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Саморезы 4.2×55 к лагам</t>
+          <t>Саморезы 4.2×65 к лагам</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1797,7 +1797,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="F36" s="10">
         <f>IF(D36="","",D36*E36)</f>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>черновой настил</t>
+          <t>черновой настил 22 мм</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Фанера ФСФ 12 мм поверх пластин ТП — под ламинат</t>
+          <t>OSB-3 12 мм поверх пластин ТП — под ламинат</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -1832,7 +1832,7 @@
         <v/>
       </c>
       <c r="E37" s="14" t="n">
-        <v>2190</v>
+        <v>1250</v>
       </c>
       <c r="F37" s="15">
         <f>IF(D37="","",D37*E37)</f>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>на этот слой: подложка 1–2 мм и ламинат</t>
+          <t>на этот слой: подложка 1–2 мм и ламинат; фанера не закладывается</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Саморезы 3.5×41 + клей по дереву на настил 12 мм</t>
+          <t>Саморезы 3.5×41 + клей по дереву на OSB 12 мм</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>фанера жилых + ГВЛВ с/у</t>
+          <t>OSB жилых + ГВЛВ с/у</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr"/>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>класть на фанеру 12 мм, не на пластины</t>
+          <t>класть на OSB 12 мм, не на пластины</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
     <row r="17">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>Пластина VT.FP.SZ.0125 = 1000×125 мм, труба Ø16. Пачка 40 шт. Норма 6.4 шт/м² ≈ 80% покрытия (на петлях пластин нет). Контур не длиннее 80–90 м — отсюда число петель. Пол уже утеплён и под плёнкой: подложку под пластины не закладывал. Сверху на пластины — фанера 12 мм (жилые) / ГВЛВ (с/у), затем финиш. Не класть ламинат на пластины.</t>
+          <t>Пластина VT.FP.SZ.0125 = 1000×125 мм, труба Ø16. Пачка 40 шт. Норма 6.4 шт/м² ≈ 80% покрытия (на петлях пластин нет). Контур не длиннее 80–90 м — отсюда число петель. Пол уже утеплён и под плёнкой: подложку под пластины не закладывал. Сверху на пластины — OSB-3 12 мм (жилые) / ГВЛВ (с/у), затем финиш. Не класть ламинат на пластины.</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
     <row r="18">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>Не входит в итог: работы; окна; двери; утеплитель и плёнка наружных стен, пола и потолка; каркасы перегородок; терраса; кухня (гарнитур, мойка, плита, вытяжка). Ламинат кладётся на фанеру 12 мм поверх пластин ТП, не на пластины.</t>
+          <t>Не входит в итог: работы; окна; двери; утеплитель и плёнка наружных стен, пола и потолка; каркасы перегородок; терраса; кухня (гарнитур, мойка, плита, вытяжка). Ламинат кладётся на OSB-3 12 мм поверх пластин ТП, не на пластины. Фанеры нет.</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
     <row r="34">
       <c r="A34" s="34" t="inlineStr">
         <is>
-          <t>Пирог пола: черновой настил → пластины ТП → фанера 12 мм → подложка → ламинат; в с/у ГВЛВ + плитка</t>
+          <t>Пирог пола: OSB-3 22 мм → пластины ТП → OSB-3 12 мм → подложка → ламинат; в с/у ГВЛВ + плитка</t>
         </is>
       </c>
     </row>
@@ -6487,9 +6487,9 @@
       <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Пирог дальше уже сделанного (лаги + утеплитель + плёнка):
-1) Черновой настил OSB-3 / фанера ФСФ 18 мм по лагам — если под плёнкой ещё дырки между лагами. Если черновой пол уже лежит — эту строку в смете обнулить.
+1) Черновой настил OSB-3 22 мм по лагам — если под плёнкой ещё дырки между лагами. Если черновой пол уже лежит — эту строку в смете обнулить.
 2) Пластины VT.FP.SZ + труба 16 мм (вкладка Теплый_пол).
-3) Сплошной настил поверх пластин: фанера ФСФ 12 мм в жилых — на НЕЁ кладётся тонкая подложка и ламинат. Прямо на алюминиевые пластины ламинат нельзя: трубы и кромки плит продавят замки.
+3) Второй слой OSB-3 12 мм поверх пластин в жилых — на НЕГО кладётся тонкая подложка и ламинат. Фанера не нужна: OSB дешевле и тот же сплошной щит. Прямо на пластины ламинат нельзя.
 4) В с/у поверх труб — 2 слоя ГВЛВ 10 мм, затем гидроизоляция и плитка.
 5) Подложка под ламинат только 1–2 мм «для ТП», без толстой пробки.</t>
         </is>

--- a/barnhouse/smeta_barnhouse_pod_kluch.xlsx
+++ b/barnhouse/smeta_barnhouse_pod_kluch.xlsx
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>свет, розетки, стиралка, котёл, бойлер</t>
+          <t>свет, розетки, стиралка, бойлер, котёл</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг-LS 3×4 (котёл / бойлер)</t>
+          <t>Кабель ВВГнг-LS 3×4 (бойлер)</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -3794,7 +3794,7 @@
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>Как пользоваться: меняйте столбец «Цена, ₽» — сумма раздела и итог пересчитаются. Количество с формулой тянется с вкладок Полы / Стены / Потолки / Обшивка / Теплый_пол / С_у. Строки техники (котёл, бойлер) обнулите в «Кол-во», если привезёте своё. Работы, окна, двери, утепление и плёнка наружного контура, каркасы перегородок и вся терраса в смету не входят. Цены — ориентир Петрович СПб / Valtec, сентябрь 2026; перед закупкой сверьте карточку товара. Отделка: МДФ дуб альпийский 2600×238×6 (Союз), без лака — покрытие уже на панели. Кухня (гарнитур, мойка, плита, вытяжка, смеситель) в смету не входит.</t>
+          <t>Как пользоваться: меняйте столбец «Цена, ₽» — сумма раздела и итог пересчитаются. Количество с формулой тянется с вкладок Полы / Стены / Потолки / Обшивка / С_у. Строки техники (котёл, бойлер) обнулите в «Кол-во», если привезёте своё. Работы, окна, двери, утепление и плёнка наружного контура, каркасы перегородок и вся терраса в смету не входят. Цены — ориентир Петрович СПб / Valtec, сентябрь 2026; перед закупкой сверьте карточку товара. Отделка: МДФ дуб альпийский 2600×238×6 (Союз), без лака — покрытие уже на панели. Кухня (гарнитур, мойка, плита, вытяжка, смеситель) в смету не входит.</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="B15" s="39">
-        <f>Теплый_пол!D12</f>
+        <f>Теплый_пол!B12</f>
         <v/>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>нет / не трогаем</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Контур ТП</t>
+          <t>Отопление пола</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
